--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdCommandsCollection001_F10.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdCommandsCollection001_F10.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="1020" windowWidth="13020" windowHeight="4320"/>
@@ -25,10 +25,6 @@
     <t>币种</t>
   </si>
   <si>
-    <t>标的资产代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>券面总额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -38,6 +34,10 @@
   </si>
   <si>
     <t>期限（天）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>质押标的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -48,7 +48,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -59,7 +59,16 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -82,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -91,6 +100,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -101,12 +113,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -148,7 +163,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -183,7 +198,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -393,27 +408,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.625" customWidth="1"/>
-    <col min="2" max="2" width="12.625" customWidth="1"/>
-    <col min="3" max="4" width="15.625" customWidth="1"/>
-    <col min="5" max="5" width="14.875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.625" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="18.6328125" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" customWidth="1"/>
+    <col min="3" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="16.375" customWidth="1"/>
-    <col min="12" max="12" width="17.375" customWidth="1"/>
-    <col min="13" max="13" width="14.25" customWidth="1"/>
-    <col min="14" max="14" width="15.125" customWidth="1"/>
-    <col min="15" max="15" width="15.25" customWidth="1"/>
-    <col min="16" max="16" width="14.5" customWidth="1"/>
+    <col min="9" max="10" width="17.90625" customWidth="1"/>
+    <col min="11" max="11" width="16.36328125" customWidth="1"/>
+    <col min="12" max="12" width="17.36328125" customWidth="1"/>
+    <col min="13" max="13" width="14.26953125" customWidth="1"/>
+    <col min="14" max="14" width="15.08984375" customWidth="1"/>
+    <col min="15" max="15" width="15.26953125" customWidth="1"/>
+    <col min="16" max="16" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -422,13 +437,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
